--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Design Configurations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCF868BD-3134-4743-A0C8-453EADB29DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47783856-919A-4941-9BFF-081CD0596248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="520" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
+    <workbookView xWindow="260" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="3" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>
@@ -1088,13 +1088,13 @@
     <t>Prop_Dia</t>
   </si>
   <si>
-    <t>Snr_Proj_v1</t>
-  </si>
-  <si>
     <t>SD7062</t>
   </si>
   <si>
     <t>NACA0021</t>
+  </si>
+  <si>
+    <t>JB_V1</t>
   </si>
 </sst>
 </file>
@@ -3945,7 +3945,7 @@
     </row>
     <row r="6" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>237</v>
@@ -4971,10 +4971,10 @@
     </row>
     <row r="6" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>242</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>243</v>
       </c>
       <c r="C6" s="10">
         <v>0.14000000000000001</v>
@@ -5097,7 +5097,7 @@
         <v>1.7520000000000001E-2</v>
       </c>
       <c r="AQ6" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AR6" s="10">
         <v>0.21</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B6" t="s">
         <v>188</v>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47783856-919A-4941-9BFF-081CD0596248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10880EF4-17E2-F340-BD7B-0D49A326F8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="3" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
@@ -281,7 +281,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -290,12 +290,31 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Units of lb/hr/hp
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Units of lb/hr/hp
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
         </r>
       </text>
@@ -360,7 +379,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="246">
   <si>
     <t>Length_f</t>
   </si>
@@ -1095,6 +1114,9 @@
   </si>
   <si>
     <t>JB_V1</t>
+  </si>
+  <si>
+    <t>2131 W</t>
   </si>
 </sst>
 </file>
@@ -5448,7 +5470,7 @@
         <v>188</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -5464,6 +5486,18 @@
       </c>
       <c r="H6">
         <v>0</v>
+      </c>
+      <c r="I6">
+        <v>2.8576999999999999</v>
+      </c>
+      <c r="J6">
+        <v>0.39</v>
+      </c>
+      <c r="K6">
+        <v>0.7</v>
+      </c>
+      <c r="L6">
+        <v>0.75</v>
       </c>
       <c r="N6">
         <v>0.9</v>
@@ -5473,6 +5507,11 @@
       </c>
       <c r="P6">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="I7" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="19" s="21" customFormat="1" x14ac:dyDescent="0.2"/>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10880EF4-17E2-F340-BD7B-0D49A326F8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7ECB4F-B8A6-9C46-9BC2-8B21D544B142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="260" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="3" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
@@ -5499,6 +5499,9 @@
       <c r="L6">
         <v>0.75</v>
       </c>
+      <c r="M6">
+        <v>300</v>
+      </c>
       <c r="N6">
         <v>0.9</v>
       </c>
@@ -5507,6 +5510,13 @@
       </c>
       <c r="P6">
         <v>0.9</v>
+      </c>
+      <c r="Q6">
+        <f>M6*N6*O6*P6</f>
+        <v>218.70000000000002</v>
+      </c>
+      <c r="R6">
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7ECB4F-B8A6-9C46-9BC2-8B21D544B142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D077953F-200C-B54A-93A7-B0F5E120B905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="260" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="3" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
+    <workbookView xWindow="260" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="2" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>
@@ -379,7 +379,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="243">
   <si>
     <t>Length_f</t>
   </si>
@@ -921,9 +921,6 @@
     <t>Max mach for design.</t>
   </si>
   <si>
-    <t>F16</t>
-  </si>
-  <si>
     <t>NACA0004</t>
   </si>
   <si>
@@ -1020,9 +1017,6 @@
     <t>Military_Cargo/Bomber</t>
   </si>
   <si>
-    <t>C172</t>
-  </si>
-  <si>
     <t>NACA2412</t>
   </si>
   <si>
@@ -1101,9 +1095,6 @@
     <t>PROP_Turboprop</t>
   </si>
   <si>
-    <t>Tiltrotor Turboprop</t>
-  </si>
-  <si>
     <t>Prop_Dia</t>
   </si>
   <si>
@@ -1113,10 +1104,10 @@
     <t>NACA0021</t>
   </si>
   <si>
-    <t>JB_V1</t>
-  </si>
-  <si>
     <t>2131 W</t>
+  </si>
+  <si>
+    <t>JB_{V1}</t>
   </si>
 </sst>
 </file>
@@ -2109,7 +2100,7 @@
         <v>58</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="32" x14ac:dyDescent="0.2">
@@ -2263,7 +2254,7 @@
         <v>58</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="32" x14ac:dyDescent="0.2">
@@ -2773,7 +2764,7 @@
         <v>58</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -3050,7 +3041,7 @@
     </row>
     <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B72" s="3" t="str" cm="1">
         <f t="array" ref="B72:B82">TRANSPOSE([1]Propulsion!A1:K1)</f>
@@ -3060,12 +3051,12 @@
         <v>58</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B73" s="3" t="str">
         <v>PropType</v>
@@ -3074,12 +3065,12 @@
         <v>58</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B74" s="3" t="str">
         <v>Number</v>
@@ -3088,68 +3079,68 @@
         <v>58</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B75" s="3" t="str">
         <v>TA_mil_sl</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B76" s="3" t="str">
         <v>TSFC_mil_sl</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B77" s="3" t="str">
         <v>TA_AB_sl</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B78" s="3" t="str">
         <v>TSFC_AB_sl</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B79" s="3" t="str">
         <v>Install_loss</v>
@@ -3158,40 +3149,40 @@
         <v>58</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B80" s="3" t="str">
         <v>PA_shp_sl</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B81" s="3" t="str">
         <v>SFC_sl</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B82" s="3" t="str">
         <v>Prop_eff</v>
@@ -3200,7 +3191,7 @@
         <v>58</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -3210,7 +3201,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ADD393-55AB-49FB-9382-D2896E9EB980}">
-  <dimension ref="A1:AV19"/>
+  <dimension ref="A1:AV16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="4"/>
@@ -3234,7 +3225,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>5</v>
@@ -3377,83 +3368,83 @@
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="C2" s="4">
         <v>0</v>
       </c>
       <c r="D2" s="4">
-        <v>0.85</v>
+        <v>0.18</v>
       </c>
       <c r="E2" s="4">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="F2" s="4">
-        <v>46.5</v>
+        <v>27</v>
       </c>
       <c r="G2" s="4">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H6" si="0">F2/G2</f>
-        <v>10.333333333333334</v>
+        <f t="shared" ref="H2:H3" si="0">F2/G2</f>
+        <v>6.75</v>
       </c>
       <c r="I2" s="4">
-        <v>22.49</v>
+        <v>12.56</v>
       </c>
       <c r="J2" s="4">
-        <v>13.853999999999999</v>
+        <v>0</v>
       </c>
       <c r="K2" s="4">
-        <v>657.38</v>
+        <v>280</v>
       </c>
       <c r="L2" s="4">
         <v>1</v>
       </c>
       <c r="M2" s="4">
-        <v>2.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="N2" s="4">
-        <v>300</v>
+        <v>174</v>
       </c>
       <c r="O2" s="4">
-        <v>451.24</v>
+        <v>380</v>
       </c>
       <c r="P2" s="4">
-        <v>3</v>
+        <v>7.32</v>
       </c>
       <c r="Q2" s="4">
-        <v>0.21</v>
+        <v>0.67200000000000004</v>
       </c>
       <c r="R2" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S2" s="4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T2" s="4">
         <v>1.1000000000000001</v>
       </c>
       <c r="U2" s="4">
-        <v>123.83</v>
+        <v>36.6</v>
       </c>
       <c r="V2" s="4">
-        <v>149.99</v>
+        <v>80</v>
       </c>
       <c r="W2" s="4">
-        <v>2.5670000000000002</v>
+        <v>3.5</v>
       </c>
       <c r="X2" s="4">
-        <v>0.28000000000000003</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="Y2" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="4">
-        <v>7.68</v>
+        <v>3.61</v>
       </c>
       <c r="AA2" s="4">
         <v>1.1000000000000001</v>
@@ -3480,22 +3471,22 @@
         <v>0</v>
       </c>
       <c r="AI2" s="4">
-        <v>64</v>
+        <v>11.2</v>
       </c>
       <c r="AJ2" s="4">
-        <v>80.959999999999994</v>
+        <v>25</v>
       </c>
       <c r="AK2" s="4">
         <v>1.6</v>
       </c>
       <c r="AL2" s="4">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="AM2" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AN2" s="4">
-        <v>7.22</v>
+        <v>4</v>
       </c>
       <c r="AO2" s="4">
         <v>1.1000000000000001</v>
@@ -3523,57 +3514,60 @@
       </c>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>213</v>
+      <c r="A3" t="s">
+        <v>242</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C3" s="4">
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <v>0.18</v>
+        <v>4.7300000000000002E-2</v>
       </c>
       <c r="E3" s="4">
-        <v>0.3</v>
+        <v>0.20810000000000001</v>
       </c>
       <c r="F3" s="4">
-        <v>27</v>
+        <v>3.9470000000000001</v>
       </c>
       <c r="G3" s="4">
-        <v>4</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" si="0"/>
-        <v>6.75</v>
+        <v>8.0223577235772368</v>
       </c>
       <c r="I3" s="4">
-        <v>12.56</v>
+        <f>PI()*(G3/2)^2</f>
+        <v>0.19011662102463991</v>
       </c>
       <c r="J3" s="4">
         <v>0</v>
       </c>
       <c r="K3" s="4">
-        <v>280</v>
+        <f>F3*G3</f>
+        <v>1.941924</v>
       </c>
       <c r="L3" s="4">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>174</v>
+        <v>10.7639</v>
       </c>
       <c r="O3" s="4">
-        <v>380</v>
+        <f>2*N3</f>
+        <v>21.527799999999999</v>
       </c>
       <c r="P3" s="4">
-        <v>7.32</v>
+        <v>4.76</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.67200000000000004</v>
+        <v>0</v>
       </c>
       <c r="R3" s="4">
         <v>0</v>
@@ -3582,28 +3576,29 @@
         <v>0</v>
       </c>
       <c r="T3" s="4">
-        <v>1.1000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="U3" s="4">
-        <v>36.6</v>
+        <v>6.7270000000000003</v>
       </c>
       <c r="V3" s="4">
-        <v>80</v>
+        <f>U3*2</f>
+        <v>13.454000000000001</v>
       </c>
       <c r="W3" s="4">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="X3" s="4">
-        <v>0.56999999999999995</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="4">
         <v>0</v>
       </c>
       <c r="Z3" s="4">
-        <v>3.61</v>
+        <v>1.498</v>
       </c>
       <c r="AA3" s="4">
-        <v>1.1000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="AB3" s="4">
         <v>0</v>
@@ -3627,10 +3622,11 @@
         <v>0</v>
       </c>
       <c r="AI3" s="4">
-        <v>11.2</v>
+        <v>1.4962</v>
       </c>
       <c r="AJ3" s="4">
-        <v>25</v>
+        <f>2*AI3</f>
+        <v>2.9923999999999999</v>
       </c>
       <c r="AK3" s="4">
         <v>1.6</v>
@@ -3642,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="AN3" s="4">
-        <v>4</v>
+        <v>0.37140000000000001</v>
       </c>
       <c r="AO3" s="4">
         <v>1.1000000000000001</v>
@@ -3669,455 +3665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.18</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="F4" s="4">
-        <v>27</v>
-      </c>
-      <c r="G4" s="4">
-        <v>4</v>
-      </c>
-      <c r="H4" s="4">
-        <f t="shared" si="0"/>
-        <v>6.75</v>
-      </c>
-      <c r="I4" s="4">
-        <v>12.56</v>
-      </c>
-      <c r="J4" s="4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4">
-        <v>280</v>
-      </c>
-      <c r="L4" s="4">
-        <v>1</v>
-      </c>
-      <c r="M4" s="4">
-        <v>1</v>
-      </c>
-      <c r="N4" s="4">
-        <v>174</v>
-      </c>
-      <c r="O4" s="4">
-        <v>380</v>
-      </c>
-      <c r="P4" s="4">
-        <v>7.32</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>0.67200000000000004</v>
-      </c>
-      <c r="R4" s="4">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="U4" s="4">
-        <v>36.6</v>
-      </c>
-      <c r="V4" s="4">
-        <v>80</v>
-      </c>
-      <c r="W4" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="X4" s="4">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="Y4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="4">
-        <v>3.61</v>
-      </c>
-      <c r="AA4" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="AB4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="4">
-        <v>11.2</v>
-      </c>
-      <c r="AJ4" s="4">
-        <v>25</v>
-      </c>
-      <c r="AK4" s="4">
-        <v>1.6</v>
-      </c>
-      <c r="AL4" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="AM4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="4">
-        <v>4</v>
-      </c>
-      <c r="AO4" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="AP4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AR4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="F5" s="4">
-        <v>57</v>
-      </c>
-      <c r="G5" s="4">
-        <v>10</v>
-      </c>
-      <c r="H5" s="4">
-        <f t="shared" si="0"/>
-        <v>5.7</v>
-      </c>
-      <c r="I5" s="4">
-        <f>PI()*(G5/2)^2</f>
-        <v>78.539816339744831</v>
-      </c>
-      <c r="J5" s="4">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4">
-        <f>2500</f>
-        <v>2500</v>
-      </c>
-      <c r="L5" s="4">
-        <v>1</v>
-      </c>
-      <c r="M5" s="4">
-        <v>2</v>
-      </c>
-      <c r="N5" s="4">
-        <v>301</v>
-      </c>
-      <c r="O5" s="4">
-        <v>620</v>
-      </c>
-      <c r="P5" s="4">
-        <v>6</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="R5" s="4">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="U5" s="4">
-        <v>180</v>
-      </c>
-      <c r="V5" s="4">
-        <v>200</v>
-      </c>
-      <c r="W5" s="4">
-        <v>3</v>
-      </c>
-      <c r="X5" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="Y5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="4">
-        <v>10</v>
-      </c>
-      <c r="AA5" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="AB5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="4">
-        <v>100</v>
-      </c>
-      <c r="AJ5" s="4">
-        <v>140</v>
-      </c>
-      <c r="AK5" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="AL5" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="AM5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="4">
-        <v>7</v>
-      </c>
-      <c r="AO5" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="AP5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>244</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>4.7300000000000002E-2</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.20810000000000001</v>
-      </c>
-      <c r="F6" s="4">
-        <v>3.9470000000000001</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0.49199999999999999</v>
-      </c>
-      <c r="H6" s="4">
-        <f t="shared" si="0"/>
-        <v>8.0223577235772368</v>
-      </c>
-      <c r="I6" s="4">
-        <f>PI()*(G6/2)^2</f>
-        <v>0.19011662102463991</v>
-      </c>
-      <c r="J6" s="4">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4">
-        <f>F6*G6</f>
-        <v>1.941924</v>
-      </c>
-      <c r="L6" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="M6" s="4">
-        <v>2</v>
-      </c>
-      <c r="N6" s="4">
-        <v>10.7639</v>
-      </c>
-      <c r="O6" s="4">
-        <f>2*N6</f>
-        <v>21.527799999999999</v>
-      </c>
-      <c r="P6" s="4">
-        <v>4.76</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4">
-        <v>0</v>
-      </c>
-      <c r="T6" s="4">
-        <v>1.4</v>
-      </c>
-      <c r="U6" s="4">
-        <v>6.7270000000000003</v>
-      </c>
-      <c r="V6" s="4">
-        <f>U6*2</f>
-        <v>13.454000000000001</v>
-      </c>
-      <c r="W6" s="4">
-        <v>3</v>
-      </c>
-      <c r="X6" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="4">
-        <v>1.498</v>
-      </c>
-      <c r="AA6" s="4">
-        <v>1.4</v>
-      </c>
-      <c r="AB6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="4">
-        <v>1.4962</v>
-      </c>
-      <c r="AJ6" s="4">
-        <f>2*AI6</f>
-        <v>2.9923999999999999</v>
-      </c>
-      <c r="AK6" s="4">
-        <v>1.6</v>
-      </c>
-      <c r="AL6" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="AM6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="4">
-        <v>0.37140000000000001</v>
-      </c>
-      <c r="AO6" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="AP6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV6" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" s="22" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:48" s="22" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -4127,7 +3675,7 @@
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$19</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B18</xm:sqref>
+          <xm:sqref>B2:B15</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4137,7 +3685,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{538960B4-04F0-4DA1-BF31-3569558CC234}">
-  <dimension ref="A1:BB19"/>
+  <dimension ref="A1:BB16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" style="10" customWidth="1"/>
@@ -4322,133 +3870,137 @@
     <row r="2" spans="1:54" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="str">
         <f>Main_Input!A2</f>
-        <v>F16</v>
+        <v>Electric</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="C2" s="10">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="D2" s="10">
         <v>0.3</v>
       </c>
-      <c r="E2" s="29">
-        <v>-0.54879999999999995</v>
+      <c r="E2" s="3">
+        <f>-0.483</f>
+        <v>-0.48299999999999998</v>
       </c>
       <c r="F2" s="29">
-        <v>-0.44479999999999997</v>
+        <f>-0.3983</f>
+        <v>-0.39829999999999999</v>
       </c>
       <c r="G2" s="29">
-        <v>-0.34029999999999999</v>
+        <f>-0.3108</f>
+        <v>-0.31080000000000002</v>
       </c>
       <c r="H2" s="29">
-        <v>-0.23960000000000001</v>
+        <v>-0.2485</v>
       </c>
       <c r="I2" s="29">
-        <v>-0.12509999999999999</v>
+        <v>-0.1244</v>
       </c>
       <c r="J2" s="10">
-        <v>0</v>
+        <v>-5.8900000000000001E-2</v>
       </c>
       <c r="K2" s="29">
-        <v>0.12509999999999999</v>
+        <v>0.13750000000000001</v>
       </c>
       <c r="L2" s="29">
-        <v>0.2394</v>
+        <v>0.30249999999999999</v>
       </c>
       <c r="M2" s="29">
-        <v>0.34010000000000001</v>
+        <v>0.45279999999999998</v>
       </c>
       <c r="N2" s="29">
-        <v>0.4446</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="O2" s="29">
-        <v>0.54869999999999997</v>
+        <v>0.7429</v>
       </c>
       <c r="P2" s="29">
-        <v>0.6462</v>
+        <v>0.85670000000000002</v>
       </c>
       <c r="Q2" s="29">
-        <v>0.73480000000000001</v>
+        <v>0.95979999999999999</v>
       </c>
       <c r="R2" s="10">
-        <v>0.8</v>
+        <v>1.0251999999999999</v>
       </c>
       <c r="S2" s="10">
-        <v>0.93</v>
+        <v>1.0969</v>
       </c>
       <c r="T2" s="29">
-        <v>0.71640000000000004</v>
+        <v>1.1591</v>
       </c>
       <c r="U2" s="29">
-        <v>0.71740000000000004</v>
+        <v>1.1391</v>
       </c>
       <c r="V2" s="10">
-        <v>0.7</v>
+        <v>1.0009999999999999</v>
       </c>
       <c r="W2" s="10">
-        <v>0.93</v>
+        <f>1.1591</f>
+        <v>1.1591</v>
       </c>
       <c r="X2" s="29">
-        <v>9.9399999999999992E-3</v>
+        <v>3.1399999999999997E-2</v>
       </c>
       <c r="Y2" s="29">
-        <v>8.1200000000000005E-3</v>
+        <v>2.6689999999999998E-2</v>
       </c>
       <c r="Z2" s="29">
-        <v>7.3699999999999998E-3</v>
+        <v>2.6689999999999998E-2</v>
       </c>
       <c r="AA2" s="29">
-        <v>5.7000000000000002E-3</v>
+        <v>2.1329999999999998E-2</v>
       </c>
       <c r="AB2" s="29">
-        <v>4.2599999999999999E-3</v>
+        <v>2.1909999999999999E-2</v>
       </c>
       <c r="AC2" s="29">
-        <v>3.3800000000000002E-3</v>
+        <v>2.4060000000000002E-2</v>
       </c>
       <c r="AD2" s="29">
-        <v>4.2599999999999999E-3</v>
+        <v>2.81E-2</v>
       </c>
       <c r="AE2" s="29">
-        <v>5.7000000000000002E-3</v>
+        <v>3.099E-2</v>
       </c>
       <c r="AF2" s="29">
-        <v>7.3699999999999998E-3</v>
+        <v>3.304E-2</v>
       </c>
       <c r="AG2" s="29">
-        <v>8.1200000000000005E-3</v>
+        <v>3.3750000000000002E-2</v>
       </c>
       <c r="AH2" s="29">
-        <v>9.9600000000000001E-3</v>
+        <v>3.2559999999999999E-2</v>
       </c>
       <c r="AI2" s="29">
-        <v>0.01</v>
+        <v>3.159E-2</v>
       </c>
       <c r="AJ2" s="29">
-        <v>2.034E-2</v>
+        <v>3.0269999999999998E-2</v>
       </c>
       <c r="AK2" s="11">
-        <v>0.03</v>
+        <v>3.245E-2</v>
       </c>
       <c r="AL2" s="11">
-        <v>0.05</v>
+        <v>3.9794999999999997E-2</v>
       </c>
       <c r="AM2" s="29">
-        <v>0.1191</v>
+        <v>4.9970000000000001E-2</v>
       </c>
       <c r="AN2" s="29">
-        <v>0.12388</v>
+        <v>6.5100000000000005E-2</v>
       </c>
       <c r="AO2" s="11">
-        <v>0.15</v>
+        <v>9.2009999999999995E-2</v>
       </c>
       <c r="AP2" s="29">
-        <v>3.3800000000000002E-3</v>
+        <v>2.1329999999999998E-2</v>
       </c>
       <c r="AQ2" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AR2" s="10">
         <v>0.04</v>
@@ -4466,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="AW2" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AX2" s="10">
         <v>0.04</v>
@@ -4484,143 +4036,138 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:54" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="str">
-        <f>Main_Input!A3</f>
-        <v>C172</v>
+    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>242</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="C3" s="10">
-        <v>0.12</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D3" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="E3" s="3">
-        <f>-0.483</f>
-        <v>-0.48299999999999998</v>
-      </c>
-      <c r="F3" s="29">
-        <f>-0.3983</f>
-        <v>-0.39829999999999999</v>
-      </c>
-      <c r="G3" s="29">
-        <f>-0.3108</f>
-        <v>-0.31080000000000002</v>
-      </c>
-      <c r="H3" s="29">
-        <v>-0.2485</v>
-      </c>
-      <c r="I3" s="29">
-        <v>-0.1244</v>
+        <v>0.255</v>
+      </c>
+      <c r="E3" s="10">
+        <v>-0.1431</v>
+      </c>
+      <c r="F3" s="10">
+        <v>-5.0000000000000001E-3</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0.10730000000000001</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0.20549999999999999</v>
+      </c>
+      <c r="I3" s="10">
+        <v>0.29360000000000003</v>
       </c>
       <c r="J3" s="10">
-        <v>-5.8900000000000001E-2</v>
-      </c>
-      <c r="K3" s="29">
-        <v>0.13750000000000001</v>
-      </c>
-      <c r="L3" s="29">
-        <v>0.30249999999999999</v>
-      </c>
-      <c r="M3" s="29">
-        <v>0.45279999999999998</v>
-      </c>
-      <c r="N3" s="29">
-        <v>0.59899999999999998</v>
-      </c>
-      <c r="O3" s="29">
-        <v>0.7429</v>
-      </c>
-      <c r="P3" s="29">
-        <v>0.85670000000000002</v>
-      </c>
-      <c r="Q3" s="29">
-        <v>0.95979999999999999</v>
+        <v>0.44130000000000003</v>
+      </c>
+      <c r="K3" s="10">
+        <v>0.55389999999999995</v>
+      </c>
+      <c r="L3" s="10">
+        <v>0.6593</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0.76270000000000004</v>
+      </c>
+      <c r="N3" s="10">
+        <v>0.86850000000000005</v>
+      </c>
+      <c r="O3" s="10">
+        <v>0.97030000000000005</v>
+      </c>
+      <c r="P3" s="10">
+        <v>1.0701000000000001</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>1.1707000000000001</v>
       </c>
       <c r="R3" s="10">
-        <v>1.0251999999999999</v>
+        <v>1.2575000000000001</v>
       </c>
       <c r="S3" s="10">
-        <v>1.0969</v>
-      </c>
-      <c r="T3" s="29">
-        <v>1.1591</v>
-      </c>
-      <c r="U3" s="29">
-        <v>1.1391</v>
+        <v>1.3427</v>
+      </c>
+      <c r="T3" s="10">
+        <v>1.4209000000000001</v>
+      </c>
+      <c r="U3" s="10">
+        <v>1.4866999999999999</v>
       </c>
       <c r="V3" s="10">
-        <v>1.0009999999999999</v>
+        <v>1.5385</v>
       </c>
       <c r="W3" s="10">
-        <f>1.1591</f>
-        <v>1.1591</v>
-      </c>
-      <c r="X3" s="29">
-        <v>3.1399999999999997E-2</v>
-      </c>
-      <c r="Y3" s="29">
-        <v>2.6689999999999998E-2</v>
-      </c>
-      <c r="Z3" s="29">
-        <v>2.6689999999999998E-2</v>
-      </c>
-      <c r="AA3" s="29">
-        <v>2.1329999999999998E-2</v>
-      </c>
-      <c r="AB3" s="29">
-        <v>2.1909999999999999E-2</v>
-      </c>
-      <c r="AC3" s="29">
-        <v>2.4060000000000002E-2</v>
-      </c>
-      <c r="AD3" s="29">
-        <v>2.81E-2</v>
-      </c>
-      <c r="AE3" s="29">
-        <v>3.099E-2</v>
-      </c>
-      <c r="AF3" s="29">
-        <v>3.304E-2</v>
-      </c>
-      <c r="AG3" s="29">
-        <v>3.3750000000000002E-2</v>
-      </c>
-      <c r="AH3" s="29">
-        <v>3.2559999999999999E-2</v>
-      </c>
-      <c r="AI3" s="29">
-        <v>3.159E-2</v>
-      </c>
-      <c r="AJ3" s="29">
-        <v>3.0269999999999998E-2</v>
-      </c>
-      <c r="AK3" s="11">
-        <v>3.245E-2</v>
-      </c>
-      <c r="AL3" s="11">
-        <v>3.9794999999999997E-2</v>
-      </c>
-      <c r="AM3" s="29">
-        <v>4.9970000000000001E-2</v>
-      </c>
-      <c r="AN3" s="29">
-        <v>6.5100000000000005E-2</v>
-      </c>
-      <c r="AO3" s="11">
-        <v>9.2009999999999995E-2</v>
-      </c>
-      <c r="AP3" s="29">
-        <v>2.1329999999999998E-2</v>
+        <v>1.5978000000000001</v>
+      </c>
+      <c r="X3" s="10">
+        <v>3.032E-2</v>
+      </c>
+      <c r="Y3" s="10">
+        <v>2.435E-2</v>
+      </c>
+      <c r="Z3" s="10">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="AA3" s="10">
+        <v>1.8790000000000001E-2</v>
+      </c>
+      <c r="AB3" s="10">
+        <v>1.8429999999999998E-2</v>
+      </c>
+      <c r="AC3" s="10">
+        <v>1.7649999999999999E-2</v>
+      </c>
+      <c r="AD3" s="10">
+        <v>1.7919999999999998E-2</v>
+      </c>
+      <c r="AE3" s="10">
+        <v>1.84E-2</v>
+      </c>
+      <c r="AF3" s="10">
+        <v>1.9290000000000002E-2</v>
+      </c>
+      <c r="AG3" s="10">
+        <v>2.018E-2</v>
+      </c>
+      <c r="AH3" s="10">
+        <v>2.147E-2</v>
+      </c>
+      <c r="AI3" s="10">
+        <v>2.2919999999999999E-2</v>
+      </c>
+      <c r="AJ3" s="10">
+        <v>2.4580000000000001E-2</v>
+      </c>
+      <c r="AK3" s="10">
+        <v>2.6849999999999999E-2</v>
+      </c>
+      <c r="AL3" s="10">
+        <v>2.9309999999999999E-2</v>
+      </c>
+      <c r="AM3" s="10">
+        <v>3.2190000000000003E-2</v>
+      </c>
+      <c r="AN3" s="10">
+        <v>3.567E-2</v>
+      </c>
+      <c r="AO3" s="10">
+        <v>3.9809999999999998E-2</v>
+      </c>
+      <c r="AP3" s="10">
+        <v>1.7520000000000001E-2</v>
       </c>
       <c r="AQ3" s="10" t="s">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="AR3" s="10">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="AS3" s="10">
         <v>0.3</v>
@@ -4635,10 +4182,10 @@
         <v>0</v>
       </c>
       <c r="AW3" s="10" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="AX3" s="10">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AY3" s="10">
         <v>0.3</v>
@@ -4653,509 +4200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:54" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="str">
-        <f>Main_Input!A4</f>
-        <v>Electric</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="C4" s="10">
-        <v>0.12</v>
-      </c>
-      <c r="D4" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="E4" s="3">
-        <f>-0.483</f>
-        <v>-0.48299999999999998</v>
-      </c>
-      <c r="F4" s="29">
-        <f>-0.3983</f>
-        <v>-0.39829999999999999</v>
-      </c>
-      <c r="G4" s="29">
-        <f>-0.3108</f>
-        <v>-0.31080000000000002</v>
-      </c>
-      <c r="H4" s="29">
-        <v>-0.2485</v>
-      </c>
-      <c r="I4" s="29">
-        <v>-0.1244</v>
-      </c>
-      <c r="J4" s="10">
-        <v>-5.8900000000000001E-2</v>
-      </c>
-      <c r="K4" s="29">
-        <v>0.13750000000000001</v>
-      </c>
-      <c r="L4" s="29">
-        <v>0.30249999999999999</v>
-      </c>
-      <c r="M4" s="29">
-        <v>0.45279999999999998</v>
-      </c>
-      <c r="N4" s="29">
-        <v>0.59899999999999998</v>
-      </c>
-      <c r="O4" s="29">
-        <v>0.7429</v>
-      </c>
-      <c r="P4" s="29">
-        <v>0.85670000000000002</v>
-      </c>
-      <c r="Q4" s="29">
-        <v>0.95979999999999999</v>
-      </c>
-      <c r="R4" s="10">
-        <v>1.0251999999999999</v>
-      </c>
-      <c r="S4" s="10">
-        <v>1.0969</v>
-      </c>
-      <c r="T4" s="29">
-        <v>1.1591</v>
-      </c>
-      <c r="U4" s="29">
-        <v>1.1391</v>
-      </c>
-      <c r="V4" s="10">
-        <v>1.0009999999999999</v>
-      </c>
-      <c r="W4" s="10">
-        <f>1.1591</f>
-        <v>1.1591</v>
-      </c>
-      <c r="X4" s="29">
-        <v>3.1399999999999997E-2</v>
-      </c>
-      <c r="Y4" s="29">
-        <v>2.6689999999999998E-2</v>
-      </c>
-      <c r="Z4" s="29">
-        <v>2.6689999999999998E-2</v>
-      </c>
-      <c r="AA4" s="29">
-        <v>2.1329999999999998E-2</v>
-      </c>
-      <c r="AB4" s="29">
-        <v>2.1909999999999999E-2</v>
-      </c>
-      <c r="AC4" s="29">
-        <v>2.4060000000000002E-2</v>
-      </c>
-      <c r="AD4" s="29">
-        <v>2.81E-2</v>
-      </c>
-      <c r="AE4" s="29">
-        <v>3.099E-2</v>
-      </c>
-      <c r="AF4" s="29">
-        <v>3.304E-2</v>
-      </c>
-      <c r="AG4" s="29">
-        <v>3.3750000000000002E-2</v>
-      </c>
-      <c r="AH4" s="29">
-        <v>3.2559999999999999E-2</v>
-      </c>
-      <c r="AI4" s="29">
-        <v>3.159E-2</v>
-      </c>
-      <c r="AJ4" s="29">
-        <v>3.0269999999999998E-2</v>
-      </c>
-      <c r="AK4" s="11">
-        <v>3.245E-2</v>
-      </c>
-      <c r="AL4" s="11">
-        <v>3.9794999999999997E-2</v>
-      </c>
-      <c r="AM4" s="29">
-        <v>4.9970000000000001E-2</v>
-      </c>
-      <c r="AN4" s="29">
-        <v>6.5100000000000005E-2</v>
-      </c>
-      <c r="AO4" s="11">
-        <v>9.2009999999999995E-2</v>
-      </c>
-      <c r="AP4" s="29">
-        <v>2.1329999999999998E-2</v>
-      </c>
-      <c r="AQ4" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="AR4" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="AS4" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AT4" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU4" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV4" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW4" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="AX4" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="AY4" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AZ4" s="10">
-        <v>0</v>
-      </c>
-      <c r="BA4" s="10">
-        <v>0</v>
-      </c>
-      <c r="BB4" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:54" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="str">
-        <f>Main_Input!A5</f>
-        <v>Tiltrotor Turboprop</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="C5" s="10">
-        <v>0.12</v>
-      </c>
-      <c r="D5" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="E5" s="3">
-        <f>-0.483</f>
-        <v>-0.48299999999999998</v>
-      </c>
-      <c r="F5" s="29">
-        <f>-0.3983</f>
-        <v>-0.39829999999999999</v>
-      </c>
-      <c r="G5" s="29">
-        <f>-0.3108</f>
-        <v>-0.31080000000000002</v>
-      </c>
-      <c r="H5" s="29">
-        <v>-0.2485</v>
-      </c>
-      <c r="I5" s="29">
-        <v>-0.1244</v>
-      </c>
-      <c r="J5" s="10">
-        <v>-5.8900000000000001E-2</v>
-      </c>
-      <c r="K5" s="29">
-        <v>0.13750000000000001</v>
-      </c>
-      <c r="L5" s="29">
-        <v>0.30249999999999999</v>
-      </c>
-      <c r="M5" s="29">
-        <v>0.45279999999999998</v>
-      </c>
-      <c r="N5" s="29">
-        <v>0.59899999999999998</v>
-      </c>
-      <c r="O5" s="29">
-        <v>0.7429</v>
-      </c>
-      <c r="P5" s="29">
-        <v>0.85670000000000002</v>
-      </c>
-      <c r="Q5" s="29">
-        <v>0.95979999999999999</v>
-      </c>
-      <c r="R5" s="10">
-        <v>1.0251999999999999</v>
-      </c>
-      <c r="S5" s="10">
-        <v>1.0969</v>
-      </c>
-      <c r="T5" s="29">
-        <v>1.1591</v>
-      </c>
-      <c r="U5" s="29">
-        <v>1.1391</v>
-      </c>
-      <c r="V5" s="10">
-        <v>1.0009999999999999</v>
-      </c>
-      <c r="W5" s="10">
-        <f>1.1591</f>
-        <v>1.1591</v>
-      </c>
-      <c r="X5" s="29">
-        <v>3.1399999999999997E-2</v>
-      </c>
-      <c r="Y5" s="29">
-        <v>2.6689999999999998E-2</v>
-      </c>
-      <c r="Z5" s="29">
-        <v>2.6689999999999998E-2</v>
-      </c>
-      <c r="AA5" s="29">
-        <v>2.1329999999999998E-2</v>
-      </c>
-      <c r="AB5" s="29">
-        <v>2.1909999999999999E-2</v>
-      </c>
-      <c r="AC5" s="29">
-        <v>2.4060000000000002E-2</v>
-      </c>
-      <c r="AD5" s="29">
-        <v>2.81E-2</v>
-      </c>
-      <c r="AE5" s="29">
-        <v>3.099E-2</v>
-      </c>
-      <c r="AF5" s="29">
-        <v>3.304E-2</v>
-      </c>
-      <c r="AG5" s="29">
-        <v>3.3750000000000002E-2</v>
-      </c>
-      <c r="AH5" s="29">
-        <v>3.2559999999999999E-2</v>
-      </c>
-      <c r="AI5" s="29">
-        <v>3.159E-2</v>
-      </c>
-      <c r="AJ5" s="29">
-        <v>3.0269999999999998E-2</v>
-      </c>
-      <c r="AK5" s="11">
-        <v>3.245E-2</v>
-      </c>
-      <c r="AL5" s="11">
-        <v>3.9794999999999997E-2</v>
-      </c>
-      <c r="AM5" s="29">
-        <v>4.9970000000000001E-2</v>
-      </c>
-      <c r="AN5" s="29">
-        <v>6.5100000000000005E-2</v>
-      </c>
-      <c r="AO5" s="11">
-        <v>9.2009999999999995E-2</v>
-      </c>
-      <c r="AP5" s="29">
-        <v>2.1329999999999998E-2</v>
-      </c>
-      <c r="AQ5" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="AR5" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="AS5" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AT5" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV5" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW5" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="AX5" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="AY5" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AZ5" s="10">
-        <v>0</v>
-      </c>
-      <c r="BA5" s="10">
-        <v>0</v>
-      </c>
-      <c r="BB5" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>244</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="C6" s="10">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0.255</v>
-      </c>
-      <c r="E6" s="10">
-        <v>-0.1431</v>
-      </c>
-      <c r="F6" s="10">
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="G6" s="10">
-        <v>0.10730000000000001</v>
-      </c>
-      <c r="H6" s="10">
-        <v>0.20549999999999999</v>
-      </c>
-      <c r="I6" s="10">
-        <v>0.29360000000000003</v>
-      </c>
-      <c r="J6" s="10">
-        <v>0.44130000000000003</v>
-      </c>
-      <c r="K6" s="10">
-        <v>0.55389999999999995</v>
-      </c>
-      <c r="L6" s="10">
-        <v>0.6593</v>
-      </c>
-      <c r="M6" s="10">
-        <v>0.76270000000000004</v>
-      </c>
-      <c r="N6" s="10">
-        <v>0.86850000000000005</v>
-      </c>
-      <c r="O6" s="10">
-        <v>0.97030000000000005</v>
-      </c>
-      <c r="P6" s="10">
-        <v>1.0701000000000001</v>
-      </c>
-      <c r="Q6" s="10">
-        <v>1.1707000000000001</v>
-      </c>
-      <c r="R6" s="10">
-        <v>1.2575000000000001</v>
-      </c>
-      <c r="S6" s="10">
-        <v>1.3427</v>
-      </c>
-      <c r="T6" s="10">
-        <v>1.4209000000000001</v>
-      </c>
-      <c r="U6" s="10">
-        <v>1.4866999999999999</v>
-      </c>
-      <c r="V6" s="10">
-        <v>1.5385</v>
-      </c>
-      <c r="W6" s="10">
-        <v>1.5978000000000001</v>
-      </c>
-      <c r="X6" s="10">
-        <v>3.032E-2</v>
-      </c>
-      <c r="Y6" s="10">
-        <v>2.435E-2</v>
-      </c>
-      <c r="Z6" s="10">
-        <v>1.9900000000000001E-2</v>
-      </c>
-      <c r="AA6" s="10">
-        <v>1.8790000000000001E-2</v>
-      </c>
-      <c r="AB6" s="10">
-        <v>1.8429999999999998E-2</v>
-      </c>
-      <c r="AC6" s="10">
-        <v>1.7649999999999999E-2</v>
-      </c>
-      <c r="AD6" s="10">
-        <v>1.7919999999999998E-2</v>
-      </c>
-      <c r="AE6" s="10">
-        <v>1.84E-2</v>
-      </c>
-      <c r="AF6" s="10">
-        <v>1.9290000000000002E-2</v>
-      </c>
-      <c r="AG6" s="10">
-        <v>2.018E-2</v>
-      </c>
-      <c r="AH6" s="10">
-        <v>2.147E-2</v>
-      </c>
-      <c r="AI6" s="10">
-        <v>2.2919999999999999E-2</v>
-      </c>
-      <c r="AJ6" s="10">
-        <v>2.4580000000000001E-2</v>
-      </c>
-      <c r="AK6" s="10">
-        <v>2.6849999999999999E-2</v>
-      </c>
-      <c r="AL6" s="10">
-        <v>2.9309999999999999E-2</v>
-      </c>
-      <c r="AM6" s="10">
-        <v>3.2190000000000003E-2</v>
-      </c>
-      <c r="AN6" s="10">
-        <v>3.567E-2</v>
-      </c>
-      <c r="AO6" s="10">
-        <v>3.9809999999999998E-2</v>
-      </c>
-      <c r="AP6" s="10">
-        <v>1.7520000000000001E-2</v>
-      </c>
-      <c r="AQ6" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="AR6" s="10">
-        <v>0.21</v>
-      </c>
-      <c r="AS6" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AT6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW6" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="AX6" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="AY6" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="AZ6" s="10">
-        <v>0</v>
-      </c>
-      <c r="BA6" s="10">
-        <v>0</v>
-      </c>
-      <c r="BB6" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:54" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5164,7 +4209,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B77D4EB-A9CB-4E6A-B1A1-7AF90F186000}">
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
@@ -5185,22 +4230,22 @@
         <v>44</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>164</v>
       </c>
       <c r="D1" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="E1" s="18" t="s">
-        <v>190</v>
-      </c>
       <c r="F1" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1" s="18" t="s">
         <v>183</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>184</v>
       </c>
       <c r="H1" s="18" t="s">
         <v>168</v>
@@ -5215,94 +4260,92 @@
         <v>167</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M1" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="N1" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="O1" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="P1" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="Q1" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="R1" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="Q1" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="R1" s="30" t="s">
-        <v>223</v>
-      </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" t="str">
-        <f>Main_Input!A2</f>
-        <v>F16</v>
+      <c r="A2" t="s">
+        <v>215</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>17800</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>29000</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>2.0499999999999998</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>200.47499999999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" t="str">
-        <f>Main_Input!A3</f>
-        <v>C172</v>
+      <c r="A3" t="s">
+        <v>242</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -5320,211 +4363,43 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>160</v>
+        <v>2.8576999999999999</v>
       </c>
       <c r="J3">
         <v>0.39</v>
       </c>
       <c r="K3">
+        <v>0.7</v>
+      </c>
+      <c r="L3">
+        <v>0.75</v>
+      </c>
+      <c r="M3">
+        <v>300</v>
+      </c>
+      <c r="N3">
+        <v>0.9</v>
+      </c>
+      <c r="O3">
+        <v>0.9</v>
+      </c>
+      <c r="P3">
+        <v>0.9</v>
+      </c>
+      <c r="Q3">
+        <f>M3*N3*O3*P3</f>
+        <v>218.70000000000002</v>
+      </c>
+      <c r="R3">
         <v>0.8</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>160</v>
-      </c>
-      <c r="J4">
-        <v>0.39</v>
-      </c>
-      <c r="K4">
-        <v>0.8</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>275</v>
-      </c>
-      <c r="N4">
-        <v>0.9</v>
-      </c>
-      <c r="O4">
-        <v>0.9</v>
-      </c>
-      <c r="P4">
-        <v>0.9</v>
-      </c>
-      <c r="Q4">
-        <v>200.47499999999999</v>
-      </c>
-      <c r="R4">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>240</v>
-      </c>
-      <c r="B5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>6150</v>
-      </c>
-      <c r="J5">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="K5">
-        <v>0.7</v>
-      </c>
-      <c r="L5">
-        <v>38</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>244</v>
-      </c>
-      <c r="B6" t="s">
-        <v>188</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>2.8576999999999999</v>
-      </c>
-      <c r="J6">
-        <v>0.39</v>
-      </c>
-      <c r="K6">
-        <v>0.7</v>
-      </c>
-      <c r="L6">
-        <v>0.75</v>
-      </c>
-      <c r="M6">
-        <v>300</v>
-      </c>
-      <c r="N6">
-        <v>0.9</v>
-      </c>
-      <c r="O6">
-        <v>0.9</v>
-      </c>
-      <c r="P6">
-        <v>0.9</v>
-      </c>
-      <c r="Q6">
-        <f>M6*N6*O6*P6</f>
-        <v>218.70000000000002</v>
-      </c>
-      <c r="R6">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="I7" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="19" s="21" customFormat="1" x14ac:dyDescent="0.2"/>
+      <c r="I4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5535,7 +4410,7 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B18</xm:sqref>
+          <xm:sqref>B2:B15</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5555,118 +4430,118 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B7" t="s">
         <v>224</v>
-      </c>
-      <c r="B7" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" s="28" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B10" s="28" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B12" s="28" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D077953F-200C-B54A-93A7-B0F5E120B905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD4AB34-CE58-B242-AD8F-C544E00D9D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="260" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="2" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
+    <workbookView xWindow="260" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD4AB34-CE58-B242-AD8F-C544E00D9D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="260" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
+    <workbookView xWindow="260" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="2" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10909"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D36BFF3C-2576-944B-B337-F280C52B8119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{FDA0E7D9-4BE6-F948-988C-7D28C0BEF6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3324,8 +3324,8 @@
         <v>0</v>
       </c>
       <c r="K2" s="7">
-        <f>F2*G2</f>
-        <v>1.941924</v>
+        <f>2*PI()*(G2/2)*F2</f>
+        <v>6.1007341722297053</v>
       </c>
       <c r="L2" s="7">
         <v>1.1000000000000001</v>
@@ -3356,11 +3356,12 @@
         <v>1.4</v>
       </c>
       <c r="U2" s="7">
-        <v>6.7270000000000003</v>
+        <f>0.2*N2</f>
+        <v>2.1527799999999999</v>
       </c>
       <c r="V2" s="7">
         <f>U2*2</f>
-        <v>13.454000000000001</v>
+        <v>4.3055599999999998</v>
       </c>
       <c r="W2" s="7">
         <v>3</v>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10909"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{FDA0E7D9-4BE6-F948-988C-7D28C0BEF6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{0045E078-6285-7C46-AE56-B37B0673D5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -4222,10 +4222,10 @@
         <v>0</v>
       </c>
       <c r="T8" s="22">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="U8" s="22">
-        <v>0</v>
+        <v>1.9735</v>
       </c>
       <c r="V8" s="22">
         <v>1.0252624699999999</v>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10909"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{0045E078-6285-7C46-AE56-B37B0673D5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{10440731-3188-AC41-8916-A1116D4EFD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="520" windowWidth="28800" windowHeight="16220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="289">
   <si>
     <t>Worksheet</t>
   </si>
@@ -3450,7 +3450,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:BB2"/>
+  <dimension ref="A1:BB5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" style="20" customWidth="1"/>
@@ -3701,7 +3701,7 @@
         <v>1.5385</v>
       </c>
       <c r="W2" s="20">
-        <v>1.5978000000000001</v>
+        <v>2</v>
       </c>
       <c r="X2" s="20">
         <v>3.032E-2</v>
@@ -3794,6 +3794,170 @@
         <v>0</v>
       </c>
       <c r="BB2" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="20">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D5" s="20">
+        <v>0.255</v>
+      </c>
+      <c r="E5" s="20">
+        <v>-0.1431</v>
+      </c>
+      <c r="F5" s="20">
+        <v>-5.0000000000000001E-3</v>
+      </c>
+      <c r="G5" s="20">
+        <v>0.10730000000000001</v>
+      </c>
+      <c r="H5" s="20">
+        <v>0.20549999999999999</v>
+      </c>
+      <c r="I5" s="20">
+        <v>0.29360000000000003</v>
+      </c>
+      <c r="J5" s="20">
+        <v>0.44130000000000003</v>
+      </c>
+      <c r="K5" s="20">
+        <v>0.55389999999999995</v>
+      </c>
+      <c r="L5" s="20">
+        <v>0.6593</v>
+      </c>
+      <c r="M5" s="20">
+        <v>0.76270000000000004</v>
+      </c>
+      <c r="N5" s="20">
+        <v>0.86850000000000005</v>
+      </c>
+      <c r="O5" s="20">
+        <v>0.97030000000000005</v>
+      </c>
+      <c r="P5" s="20">
+        <v>1.0701000000000001</v>
+      </c>
+      <c r="Q5" s="20">
+        <v>1.1707000000000001</v>
+      </c>
+      <c r="R5" s="20">
+        <v>1.2575000000000001</v>
+      </c>
+      <c r="S5" s="20">
+        <v>1.3427</v>
+      </c>
+      <c r="T5" s="20">
+        <v>1.4209000000000001</v>
+      </c>
+      <c r="U5" s="20">
+        <v>1.4866999999999999</v>
+      </c>
+      <c r="V5" s="20">
+        <v>1.5385</v>
+      </c>
+      <c r="W5" s="20">
+        <v>1.5978000000000001</v>
+      </c>
+      <c r="X5" s="20">
+        <v>3.032E-2</v>
+      </c>
+      <c r="Y5" s="20">
+        <v>2.435E-2</v>
+      </c>
+      <c r="Z5" s="20">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="AA5" s="20">
+        <v>1.8790000000000001E-2</v>
+      </c>
+      <c r="AB5" s="20">
+        <v>1.8429999999999998E-2</v>
+      </c>
+      <c r="AC5" s="20">
+        <v>1.7649999999999999E-2</v>
+      </c>
+      <c r="AD5" s="20">
+        <v>1.7919999999999998E-2</v>
+      </c>
+      <c r="AE5" s="20">
+        <v>1.84E-2</v>
+      </c>
+      <c r="AF5" s="20">
+        <v>1.9290000000000002E-2</v>
+      </c>
+      <c r="AG5" s="20">
+        <v>2.018E-2</v>
+      </c>
+      <c r="AH5" s="20">
+        <v>2.147E-2</v>
+      </c>
+      <c r="AI5" s="20">
+        <v>2.2919999999999999E-2</v>
+      </c>
+      <c r="AJ5" s="20">
+        <v>2.4580000000000001E-2</v>
+      </c>
+      <c r="AK5" s="20">
+        <v>2.6849999999999999E-2</v>
+      </c>
+      <c r="AL5" s="20">
+        <v>2.9309999999999999E-2</v>
+      </c>
+      <c r="AM5" s="20">
+        <v>3.2190000000000003E-2</v>
+      </c>
+      <c r="AN5" s="20">
+        <v>3.567E-2</v>
+      </c>
+      <c r="AO5" s="20">
+        <v>3.9809999999999998E-2</v>
+      </c>
+      <c r="AP5" s="20">
+        <v>1.7520000000000001E-2</v>
+      </c>
+      <c r="AQ5" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="AR5" s="20">
+        <v>0.21</v>
+      </c>
+      <c r="AS5" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="AT5" s="20">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="20">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="20">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="AX5" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="AY5" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="AZ5" s="20">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="20">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="20">
         <v>0</v>
       </c>
     </row>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10909"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{10440731-3188-AC41-8916-A1116D4EFD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{7C4AF514-237C-B745-AF3B-6156E8C2C75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="520" windowWidth="28800" windowHeight="16220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="520" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="289">
   <si>
     <t>Worksheet</t>
   </si>
@@ -3798,168 +3798,7 @@
       </c>
     </row>
     <row r="5" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="C5" s="20">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D5" s="20">
-        <v>0.255</v>
-      </c>
-      <c r="E5" s="20">
-        <v>-0.1431</v>
-      </c>
-      <c r="F5" s="20">
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="G5" s="20">
-        <v>0.10730000000000001</v>
-      </c>
-      <c r="H5" s="20">
-        <v>0.20549999999999999</v>
-      </c>
-      <c r="I5" s="20">
-        <v>0.29360000000000003</v>
-      </c>
-      <c r="J5" s="20">
-        <v>0.44130000000000003</v>
-      </c>
-      <c r="K5" s="20">
-        <v>0.55389999999999995</v>
-      </c>
-      <c r="L5" s="20">
-        <v>0.6593</v>
-      </c>
-      <c r="M5" s="20">
-        <v>0.76270000000000004</v>
-      </c>
-      <c r="N5" s="20">
-        <v>0.86850000000000005</v>
-      </c>
-      <c r="O5" s="20">
-        <v>0.97030000000000005</v>
-      </c>
-      <c r="P5" s="20">
-        <v>1.0701000000000001</v>
-      </c>
-      <c r="Q5" s="20">
-        <v>1.1707000000000001</v>
-      </c>
-      <c r="R5" s="20">
-        <v>1.2575000000000001</v>
-      </c>
-      <c r="S5" s="20">
-        <v>1.3427</v>
-      </c>
-      <c r="T5" s="20">
-        <v>1.4209000000000001</v>
-      </c>
-      <c r="U5" s="20">
-        <v>1.4866999999999999</v>
-      </c>
-      <c r="V5" s="20">
-        <v>1.5385</v>
-      </c>
-      <c r="W5" s="20">
-        <v>1.5978000000000001</v>
-      </c>
-      <c r="X5" s="20">
-        <v>3.032E-2</v>
-      </c>
-      <c r="Y5" s="20">
-        <v>2.435E-2</v>
-      </c>
-      <c r="Z5" s="20">
-        <v>1.9900000000000001E-2</v>
-      </c>
-      <c r="AA5" s="20">
-        <v>1.8790000000000001E-2</v>
-      </c>
-      <c r="AB5" s="20">
-        <v>1.8429999999999998E-2</v>
-      </c>
-      <c r="AC5" s="20">
-        <v>1.7649999999999999E-2</v>
-      </c>
-      <c r="AD5" s="20">
-        <v>1.7919999999999998E-2</v>
-      </c>
-      <c r="AE5" s="20">
-        <v>1.84E-2</v>
-      </c>
-      <c r="AF5" s="20">
-        <v>1.9290000000000002E-2</v>
-      </c>
-      <c r="AG5" s="20">
-        <v>2.018E-2</v>
-      </c>
-      <c r="AH5" s="20">
-        <v>2.147E-2</v>
-      </c>
-      <c r="AI5" s="20">
-        <v>2.2919999999999999E-2</v>
-      </c>
-      <c r="AJ5" s="20">
-        <v>2.4580000000000001E-2</v>
-      </c>
-      <c r="AK5" s="20">
-        <v>2.6849999999999999E-2</v>
-      </c>
-      <c r="AL5" s="20">
-        <v>2.9309999999999999E-2</v>
-      </c>
-      <c r="AM5" s="20">
-        <v>3.2190000000000003E-2</v>
-      </c>
-      <c r="AN5" s="20">
-        <v>3.567E-2</v>
-      </c>
-      <c r="AO5" s="20">
-        <v>3.9809999999999998E-2</v>
-      </c>
-      <c r="AP5" s="20">
-        <v>1.7520000000000001E-2</v>
-      </c>
-      <c r="AQ5" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="AR5" s="20">
-        <v>0.21</v>
-      </c>
-      <c r="AS5" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="AT5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AV5" s="20">
-        <v>0</v>
-      </c>
-      <c r="AW5" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="AX5" s="20">
-        <v>0.1</v>
-      </c>
-      <c r="AY5" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="AZ5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BA5" s="20">
-        <v>0</v>
-      </c>
-      <c r="BB5" s="20">
-        <v>0</v>
-      </c>
+      <c r="A5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10909"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{7C4AF514-237C-B745-AF3B-6156E8C2C75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{D70FF8EC-175D-FA4F-9BDC-7F8203BBF7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20" yWindow="520" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3334,11 +3334,12 @@
         <v>2</v>
       </c>
       <c r="N2" s="7">
-        <v>10.7639</v>
+        <f>10.7639*1.2</f>
+        <v>12.916679999999999</v>
       </c>
       <c r="O2" s="7">
         <f>2*N2</f>
-        <v>21.527799999999999</v>
+        <v>25.833359999999999</v>
       </c>
       <c r="P2" s="7">
         <v>4.76</v>
@@ -3357,11 +3358,11 @@
       </c>
       <c r="U2" s="7">
         <f>0.2*N2</f>
-        <v>2.1527799999999999</v>
+        <v>2.5833360000000001</v>
       </c>
       <c r="V2" s="7">
         <f>U2*2</f>
-        <v>4.3055599999999998</v>
+        <v>5.1666720000000002</v>
       </c>
       <c r="W2" s="7">
         <v>3</v>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10817"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{D70FF8EC-175D-FA4F-9BDC-7F8203BBF7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14141415-9AEE-B040-8F61-03D38D173453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="520" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="16220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>
@@ -17,7 +17,6 @@
     <sheet name="Geometry Reference" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -4226,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="T8" s="22">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="U8" s="22">
         <v>0</v>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10817"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14141415-9AEE-B040-8F61-03D38D173453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1252D254-2D4E-0342-873F-A1C53BC2D48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="16220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,7 +343,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="274">
   <si>
     <t>Worksheet</t>
   </si>
@@ -870,9 +870,6 @@
     <t>SkinThick_v2</t>
   </si>
   <si>
-    <t>Electric</t>
-  </si>
-  <si>
     <t>Homebuilt_Composite_Prop</t>
   </si>
   <si>
@@ -999,78 +996,33 @@
     <t>W_nose</t>
   </si>
   <si>
-    <t>Xcg_nose</t>
-  </si>
-  <si>
     <t>W_fuse</t>
   </si>
   <si>
-    <t>Xcg_fuse</t>
-  </si>
-  <si>
     <t>W_wing</t>
   </si>
   <si>
-    <t>Xcg_wing</t>
-  </si>
-  <si>
     <t>W_h1</t>
   </si>
   <si>
-    <t>Xcg_h1</t>
-  </si>
-  <si>
     <t>W_h2</t>
   </si>
   <si>
-    <t>Xcg_h2</t>
-  </si>
-  <si>
     <t>W_v1</t>
   </si>
   <si>
-    <t>Xcg_v1</t>
-  </si>
-  <si>
     <t>W_v2</t>
   </si>
   <si>
-    <t>Xcg_v2</t>
-  </si>
-  <si>
     <t>W_pay</t>
   </si>
   <si>
-    <t>Xcg_pay</t>
-  </si>
-  <si>
     <t>W_ballast</t>
   </si>
   <si>
-    <t>Xcg_ballast</t>
-  </si>
-  <si>
     <t>W_systems</t>
   </si>
   <si>
-    <t>Xcg_systems</t>
-  </si>
-  <si>
-    <t>X_LE_wing</t>
-  </si>
-  <si>
-    <t>X_LE_h1</t>
-  </si>
-  <si>
-    <t>X_LE_h2</t>
-  </si>
-  <si>
-    <t>X_LE_v1</t>
-  </si>
-  <si>
-    <t>X_LE_v2</t>
-  </si>
-  <si>
     <t>Fuse_Mat</t>
   </si>
   <si>
@@ -1095,30 +1047,6 @@
     <t>rho_LWPLA</t>
   </si>
   <si>
-    <t>rho_bulk</t>
-  </si>
-  <si>
-    <t>F16</t>
-  </si>
-  <si>
-    <t>C172</t>
-  </si>
-  <si>
-    <t>B747</t>
-  </si>
-  <si>
-    <t>T38</t>
-  </si>
-  <si>
-    <t>Tiltrotor Turboprop</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>0.0082021</t>
-  </si>
-  <si>
     <t>Prop_Dia</t>
   </si>
   <si>
@@ -1210,6 +1138,33 @@
   </si>
   <si>
     <t>UAV_Prop</t>
+  </si>
+  <si>
+    <t>Bulkhead_Mat</t>
+  </si>
+  <si>
+    <t>W_wing_spar</t>
+  </si>
+  <si>
+    <t>W_bulkhead</t>
+  </si>
+  <si>
+    <t>rho_LW_balsa</t>
+  </si>
+  <si>
+    <t>N_bulkhead</t>
+  </si>
+  <si>
+    <t>Width_bulkhead</t>
+  </si>
+  <si>
+    <t>Height_bulkhead</t>
+  </si>
+  <si>
+    <t>Depth_bulkhead</t>
+  </si>
+  <si>
+    <t>0.01312 ft</t>
   </si>
 </sst>
 </file>
@@ -3291,10 +3246,10 @@
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C2" s="7">
         <v>0</v>
@@ -3483,115 +3438,115 @@
         <v>109</v>
       </c>
       <c r="E1" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="F1" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="G1" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="H1" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="I1" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="J1" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="K1" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="L1" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="M1" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="N1" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="O1" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="P1" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="Q1" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="Q1" s="21" t="s">
+      <c r="R1" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="R1" s="21" t="s">
+      <c r="S1" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="S1" s="21" t="s">
+      <c r="T1" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="T1" s="21" t="s">
+      <c r="U1" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="U1" s="21" t="s">
+      <c r="V1" s="21" t="s">
         <v>194</v>
-      </c>
-      <c r="V1" s="21" t="s">
-        <v>195</v>
       </c>
       <c r="W1" s="21" t="s">
         <v>113</v>
       </c>
       <c r="X1" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y1" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="Y1" s="21" t="s">
+      <c r="Z1" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="Z1" s="21" t="s">
+      <c r="AA1" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="AA1" s="21" t="s">
+      <c r="AB1" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="AB1" s="21" t="s">
+      <c r="AC1" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="AC1" s="21" t="s">
+      <c r="AD1" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="AD1" s="21" t="s">
+      <c r="AE1" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="AE1" s="21" t="s">
+      <c r="AF1" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="AF1" s="21" t="s">
+      <c r="AG1" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="AG1" s="21" t="s">
+      <c r="AH1" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="AH1" s="21" t="s">
+      <c r="AI1" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="AI1" s="21" t="s">
+      <c r="AJ1" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="AJ1" s="21" t="s">
+      <c r="AK1" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="AK1" s="21" t="s">
+      <c r="AL1" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="AL1" s="21" t="s">
+      <c r="AM1" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="AM1" s="21" t="s">
+      <c r="AN1" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="AN1" s="21" t="s">
+      <c r="AO1" s="21" t="s">
         <v>212</v>
-      </c>
-      <c r="AO1" s="21" t="s">
-        <v>213</v>
       </c>
       <c r="AP1" s="21" t="s">
         <v>117</v>
@@ -3635,10 +3590,10 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C2" s="20">
         <v>0.14000000000000001</v>
@@ -3761,7 +3716,7 @@
         <v>1.7520000000000001E-2</v>
       </c>
       <c r="AQ2" s="20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AR2" s="20">
         <v>0.21</v>
@@ -3779,7 +3734,7 @@
         <v>0</v>
       </c>
       <c r="AW2" s="20" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AX2" s="20">
         <v>0.1</v>
@@ -3807,483 +3762,215 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="33" width="16" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="22" t="s">
         <v>103</v>
       </c>
       <c r="B1" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="D1" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="E1" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="F1" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="G1" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="H1" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="I1" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="J1" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="K1" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="L1" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="M1" s="22" t="s">
         <v>227</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="N1" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="O1" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="P1" s="22" t="s">
         <v>230</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="Q1" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="Q1" s="22" t="s">
+      <c r="R1" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="R1" s="22" t="s">
+      <c r="S1" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="S1" s="22" t="s">
-        <v>234</v>
-      </c>
       <c r="T1" s="22" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="U1" s="22" t="s">
-        <v>236</v>
+        <v>169</v>
       </c>
       <c r="V1" s="22" t="s">
-        <v>237</v>
+        <v>171</v>
       </c>
       <c r="W1" s="22" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="X1" s="22" t="s">
-        <v>239</v>
+        <v>173</v>
       </c>
       <c r="Y1" s="22" t="s">
-        <v>240</v>
+        <v>174</v>
       </c>
       <c r="Z1" s="22" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="AA1" s="22" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="AB1" s="22" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="AC1" s="22" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="AD1" s="22" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="AE1" s="22" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="AF1" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="AG1" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="AH1" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="AI1" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>169</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>171</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>172</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>173</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+      <c r="AG1" s="22" t="inlineStr">
+        <is>
+          <t>N_wing_spar</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="22"/>
-      <c r="Z2" s="22"/>
-      <c r="AA2" s="22"/>
-      <c r="AB2" s="22"/>
-      <c r="AC2" s="22"/>
-      <c r="AD2" s="22"/>
-      <c r="AE2" s="22"/>
-      <c r="AF2" s="22"/>
-      <c r="AG2" s="22"/>
-      <c r="AH2" s="22"/>
-      <c r="AI2" s="22"/>
-    </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="22"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="22"/>
-      <c r="Z3" s="22"/>
-      <c r="AA3" s="22"/>
-      <c r="AB3" s="22"/>
-      <c r="AC3" s="22"/>
-      <c r="AD3" s="22"/>
-      <c r="AE3" s="22"/>
-      <c r="AF3" s="22"/>
-      <c r="AG3" s="22"/>
-      <c r="AH3" s="22"/>
-      <c r="AI3" s="22"/>
-    </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
-      <c r="W4" s="22"/>
-      <c r="X4" s="22"/>
-      <c r="Y4" s="22"/>
-      <c r="Z4" s="22"/>
-      <c r="AA4" s="22"/>
-      <c r="AB4" s="22"/>
-      <c r="AC4" s="22"/>
-      <c r="AD4" s="22"/>
-      <c r="AE4" s="22"/>
-      <c r="AF4" s="22"/>
-      <c r="AG4" s="22"/>
-      <c r="AH4" s="22"/>
-      <c r="AI4" s="22"/>
-    </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="22"/>
-      <c r="V5" s="22"/>
-      <c r="W5" s="22"/>
-      <c r="X5" s="22"/>
-      <c r="Y5" s="22"/>
-      <c r="Z5" s="22"/>
-      <c r="AA5" s="22"/>
-      <c r="AB5" s="22"/>
-      <c r="AC5" s="22"/>
-      <c r="AD5" s="22"/>
-      <c r="AE5" s="22"/>
-      <c r="AF5" s="22"/>
-      <c r="AG5" s="22"/>
-      <c r="AH5" s="22"/>
-      <c r="AI5" s="22"/>
-    </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A6" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="22"/>
-      <c r="T6" s="22"/>
-      <c r="U6" s="22"/>
-      <c r="V6" s="22"/>
-      <c r="W6" s="22"/>
-      <c r="X6" s="22"/>
-      <c r="Y6" s="22"/>
-      <c r="Z6" s="22"/>
-      <c r="AA6" s="22"/>
-      <c r="AB6" s="22"/>
-      <c r="AC6" s="22"/>
-      <c r="AD6" s="22"/>
-      <c r="AE6" s="22"/>
-      <c r="AF6" s="22"/>
-      <c r="AG6" s="22"/>
-      <c r="AH6" s="22"/>
-      <c r="AI6" s="22"/>
-    </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A7" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="22"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="22"/>
-      <c r="Y7" s="22"/>
-      <c r="Z7" s="22"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="22"/>
-      <c r="AC7" s="22"/>
-      <c r="AD7" s="22"/>
-      <c r="AE7" s="22"/>
-      <c r="AF7" s="22"/>
-      <c r="AG7" s="22"/>
-      <c r="AH7" s="22"/>
-      <c r="AI7" s="22"/>
-    </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A8" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="B8" s="22">
+        <v>176</v>
+      </c>
+      <c r="B2" s="22">
         <v>0</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C2" s="22">
         <v>0</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D2" s="22">
         <v>0</v>
       </c>
-      <c r="E8" s="22">
-        <v>2.0505</v>
-      </c>
-      <c r="F8" s="22">
+      <c r="E2" s="22">
         <v>0</v>
       </c>
-      <c r="G8" s="22">
-        <v>1.2252624700000001</v>
-      </c>
-      <c r="H8" s="22">
+      <c r="F2" s="22">
         <v>0</v>
       </c>
-      <c r="I8" s="22">
-        <v>3.9</v>
-      </c>
-      <c r="J8" s="22">
+      <c r="G2" s="22">
         <v>0</v>
       </c>
-      <c r="K8" s="22">
+      <c r="H2" s="22">
         <v>0</v>
       </c>
-      <c r="L8" s="22">
+      <c r="I2" s="22">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J2" s="22">
         <v>0</v>
       </c>
-      <c r="M8" s="22">
-        <v>3.9</v>
-      </c>
-      <c r="N8" s="22">
+      <c r="K2" s="22">
+        <v>7.4</v>
+      </c>
+      <c r="L2" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="M2" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="N2" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="O2" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="P2" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q2" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="R2" t="s">
+        <v>273</v>
+      </c>
+      <c r="S2" s="22">
+        <v>37.5</v>
+      </c>
+      <c r="T2" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="U2" t="s">
+        <v>273</v>
+      </c>
+      <c r="V2" s="22">
+        <v>8.2021000000000004E-3</v>
+      </c>
+      <c r="W2" s="22">
+        <v>8.2021000000000004E-3</v>
+      </c>
+      <c r="X2" s="22">
+        <v>8.2021000000000004E-3</v>
+      </c>
+      <c r="Y2" s="22">
+        <v>8.2021000000000004E-3</v>
+      </c>
+      <c r="Z2" s="22">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="AA2" s="22">
         <v>0</v>
       </c>
-      <c r="O8" s="22">
-        <v>0</v>
-      </c>
-      <c r="P8" s="22">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="Q8" s="22">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="R8" s="22">
-        <v>0</v>
-      </c>
-      <c r="S8" s="22">
-        <v>0</v>
-      </c>
-      <c r="T8" s="22">
-        <v>7.4</v>
-      </c>
-      <c r="U8" s="22">
-        <v>0</v>
-      </c>
-      <c r="V8" s="22">
-        <v>1.0252624699999999</v>
-      </c>
-      <c r="W8" s="22">
-        <v>3.73</v>
-      </c>
-      <c r="X8" s="22">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="22">
-        <v>3.73</v>
-      </c>
-      <c r="Z8" s="22">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="AB8" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="AC8" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="AD8" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="AE8" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="AF8" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="AG8" s="22">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="AH8" s="22">
-        <v>37.5</v>
-      </c>
-      <c r="AI8" s="22"/>
-      <c r="AJ8" t="s">
-        <v>257</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>257</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>257</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>257</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>257</v>
+      <c r="AB2" s="22">
+        <v>5.5</v>
+      </c>
+      <c r="AC2" s="22">
+        <v>4</v>
+      </c>
+      <c r="AD2" s="22">
+        <v>0.3</v>
+      </c>
+      <c r="AE2" s="22">
+        <v>0.35</v>
+      </c>
+      <c r="AF2" s="22">
+        <v>0.01</v>
+      </c>
+      <c r="AG2" s="22">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4344,33 +4031,33 @@
         <v>166</v>
       </c>
       <c r="L1" s="25" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="N1" s="26" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="O1" s="26" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="P1" s="26" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="Q1" s="26" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="R1" s="26" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -4424,7 +4111,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="I3" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -4453,110 +4140,110 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="B2" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="B3" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="B4" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="B5" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="B6" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="B7" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" s="27" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B10" s="27" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B12" s="27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10920"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1252D254-2D4E-0342-873F-A1C53BC2D48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE4F188-8D8E-214E-940E-37D99651B2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="16220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>
@@ -343,7 +343,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="275">
   <si>
     <t>Worksheet</t>
   </si>
@@ -1165,6 +1165,9 @@
   </si>
   <si>
     <t>0.01312 ft</t>
+  </si>
+  <si>
+    <t>N_wing_spar</t>
   </si>
 </sst>
 </file>
@@ -3288,12 +3291,12 @@
         <v>2</v>
       </c>
       <c r="N2" s="7">
-        <f>10.7639*1.2</f>
-        <v>12.916679999999999</v>
+        <f>10.7639</f>
+        <v>10.7639</v>
       </c>
       <c r="O2" s="7">
         <f>2*N2</f>
-        <v>25.833359999999999</v>
+        <v>21.527799999999999</v>
       </c>
       <c r="P2" s="7">
         <v>4.76</v>
@@ -3312,11 +3315,11 @@
       </c>
       <c r="U2" s="7">
         <f>0.2*N2</f>
-        <v>2.5833360000000001</v>
+        <v>2.1527799999999999</v>
       </c>
       <c r="V2" s="7">
         <f>U2*2</f>
-        <v>5.1666720000000002</v>
+        <v>4.3055599999999998</v>
       </c>
       <c r="W2" s="7">
         <v>3</v>
@@ -3866,10 +3869,8 @@
       <c r="AF1" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="AG1" s="22" t="inlineStr">
-        <is>
-          <t>N_wing_spar</t>
-        </is>
+      <c r="AG1" s="22" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10920"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE4F188-8D8E-214E-940E-37D99651B2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B48507C-88D3-574D-B911-2000166293F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10927"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B48507C-88D3-574D-B911-2000166293F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D889471F-71AC-F64A-8619-20AB1BC998CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>
@@ -343,7 +343,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="274">
   <si>
     <t>Worksheet</t>
   </si>
@@ -1069,9 +1069,6 @@
   </si>
   <si>
     <t>PROP_Electric</t>
-  </si>
-  <si>
-    <t>2131 W</t>
   </si>
   <si>
     <t>PROP_Fuel</t>
@@ -3831,7 +3828,7 @@
         <v>233</v>
       </c>
       <c r="T1" s="22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="U1" s="22" t="s">
         <v>169</v>
@@ -3849,28 +3846,28 @@
         <v>174</v>
       </c>
       <c r="Z1" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="AA1" s="22" t="s">
         <v>266</v>
       </c>
-      <c r="AA1" s="22" t="s">
+      <c r="AB1" s="22" t="s">
         <v>267</v>
       </c>
-      <c r="AB1" s="22" t="s">
+      <c r="AC1" s="22" t="s">
         <v>268</v>
       </c>
-      <c r="AC1" s="22" t="s">
+      <c r="AD1" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="AD1" s="22" t="s">
+      <c r="AE1" s="22" t="s">
         <v>270</v>
       </c>
-      <c r="AE1" s="22" t="s">
+      <c r="AF1" s="22" t="s">
         <v>271</v>
       </c>
-      <c r="AF1" s="22" t="s">
-        <v>272</v>
-      </c>
       <c r="AG1" s="22" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
@@ -3926,16 +3923,16 @@
         <v>233</v>
       </c>
       <c r="R2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S2" s="22">
         <v>37.5</v>
       </c>
       <c r="T2" s="22" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="U2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="V2" s="22">
         <v>8.2021000000000004E-3</v>
@@ -3981,7 +3978,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
@@ -4091,7 +4088,7 @@
         <v>0.75</v>
       </c>
       <c r="M2">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N2">
         <v>0.9</v>
@@ -4104,15 +4101,10 @@
       </c>
       <c r="Q2">
         <f>M2*N2*O2*P2</f>
-        <v>218.70000000000002</v>
+        <v>145.80000000000001</v>
       </c>
       <c r="R2">
         <v>0.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="I3" t="s">
-        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -4141,10 +4133,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" t="s">
         <v>243</v>
-      </c>
-      <c r="B2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -4152,59 +4144,59 @@
         <v>241</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" t="s">
         <v>246</v>
-      </c>
-      <c r="B4" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B5" t="s">
         <v>248</v>
-      </c>
-      <c r="B5" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B6" t="s">
         <v>250</v>
-      </c>
-      <c r="B6" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7" t="s">
         <v>252</v>
-      </c>
-      <c r="B7" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" s="27" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B10" s="27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -4214,37 +4206,37 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10927"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D889471F-71AC-F64A-8619-20AB1BC998CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44E3BE1-7CFE-EB4B-93C6-9CA585D1FC9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4088,7 +4088,7 @@
         <v>0.75</v>
       </c>
       <c r="M2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N2">
         <v>0.9</v>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="Q2">
         <f>M2*N2*O2*P2</f>
-        <v>145.80000000000001</v>
+        <v>218.70000000000002</v>
       </c>
       <c r="R2">
         <v>0.8</v>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ZW_Snr_Proj_Initial_Design_Config.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10927"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44E3BE1-7CFE-EB4B-93C6-9CA585D1FC9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD7CD2D-2618-4D4D-B909-5F482E1F83BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>
@@ -4088,7 +4088,7 @@
         <v>0.75</v>
       </c>
       <c r="M2">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="N2">
         <v>0.9</v>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="Q2">
         <f>M2*N2*O2*P2</f>
-        <v>218.70000000000002</v>
+        <v>200.47499999999999</v>
       </c>
       <c r="R2">
         <v>0.8</v>
